--- a/examples/data/model_points_long.xlsx
+++ b/examples/data/model_points_long.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADB</t>
+          <t>adb</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -818,7 +818,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -831,7 +831,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DTH_MAIN</t>
+          <t>dth_main</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CANCER</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOSP</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>mat</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>mat</t>
         </is>
       </c>
       <c r="C21" t="n">

--- a/examples/data/model_points_long.xlsx
+++ b/examples/data/model_points_long.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>monthly_premium</t>
+          <t>level_premium</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/examples/data/model_points_long.xlsx
+++ b/examples/data/model_points_long.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>policy_id</t>
+          <t>mp_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -655,12 +655,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>policy_id</t>
+          <t>mp_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>rider_code</t>
+          <t>coverage_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
